--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753879301_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008566648607316726</v>
       </c>
       <c r="C2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>51705129</v>
+        <v>3899252</v>
       </c>
       <c r="L2" t="n">
-        <v>26874774</v>
+        <v>1625968</v>
       </c>
       <c r="M2" t="n">
-        <v>6123893</v>
+        <v>283876</v>
       </c>
       <c r="N2" t="n">
-        <v>260338</v>
+        <v>6461</v>
       </c>
       <c r="O2" t="n">
-        <v>3583920</v>
+        <v>163839</v>
       </c>
       <c r="P2" t="n">
-        <v>1361895</v>
+        <v>40970</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999849796295166</v>
+        <v>0.9999792575836182</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8222047090530396</v>
+        <v>0.7047197818756104</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6889522671699524</v>
+        <v>0.5171708464622498</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6147696971893311</v>
+        <v>0.3816553354263306</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2088054418563843</v>
+        <v>0.0483539029955864</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6668056845664978</v>
+        <v>0.4188498854637146</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7911761403083801</v>
+        <v>0.5779702663421631</v>
       </c>
       <c r="X2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="AG2" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AH2" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AI2" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556694626808167</v>
+        <v>0.9541478753089905</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118999242782593</v>
+        <v>0.9129630327224731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581674098968506</v>
+        <v>0.8576433062553406</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615565419197083</v>
+        <v>0.6601934432983398</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019808769226074</v>
+        <v>0.9016708135604858</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002053537536211935</v>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>51705129</v>
+        <v>3899252</v>
       </c>
       <c r="E3" t="n">
-        <v>7950283</v>
+        <v>971012</v>
       </c>
       <c r="F3" t="n">
-        <v>249480</v>
+        <v>47761</v>
       </c>
       <c r="G3" t="n">
-        <v>22638</v>
+        <v>4738</v>
       </c>
       <c r="H3" t="n">
-        <v>18868</v>
+        <v>5336</v>
       </c>
       <c r="I3" t="n">
-        <v>1608</v>
+        <v>385</v>
       </c>
       <c r="J3" t="n">
-        <v>120198326</v>
+        <v>10016491</v>
       </c>
       <c r="K3" t="n">
-        <v>124826168</v>
+        <v>9767289</v>
       </c>
       <c r="L3" t="n">
-        <v>144334491</v>
+        <v>11466133</v>
       </c>
       <c r="M3" t="n">
-        <v>180875973</v>
+        <v>14924143</v>
       </c>
       <c r="N3" t="n">
-        <v>193895148</v>
+        <v>16112373</v>
       </c>
       <c r="O3" t="n">
-        <v>188038434</v>
+        <v>15589281</v>
       </c>
       <c r="P3" t="n">
-        <v>193273145</v>
+        <v>16105634</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8624966740608215</v>
+        <v>0.7911624312400818</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6805927753448486</v>
+        <v>0.486021101474762</v>
       </c>
       <c r="T3" t="n">
-        <v>0.544741153717041</v>
+        <v>0.3002291917800903</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2424922734498978</v>
+        <v>0.07173389196395874</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5850412249565125</v>
+        <v>0.3193780183792114</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5863678455352783</v>
+        <v>0.2111311554908752</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="Z3" t="n">
-        <v>2363094</v>
+        <v>195844</v>
       </c>
       <c r="AA3" t="n">
-        <v>101765</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>81730</v>
+        <v>6822</v>
       </c>
       <c r="AC3" t="n">
-        <v>302</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120199464</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>133344343</v>
+        <v>11174399</v>
       </c>
       <c r="AG3" t="n">
-        <v>152997368</v>
+        <v>12694080</v>
       </c>
       <c r="AH3" t="n">
-        <v>183120991</v>
+        <v>15249719</v>
       </c>
       <c r="AI3" t="n">
-        <v>194518645</v>
+        <v>16208962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>189229252</v>
+        <v>15766212</v>
       </c>
       <c r="AK3" t="n">
-        <v>193473427</v>
+        <v>16122228</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575091600418091</v>
+        <v>0.9571381807327271</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097229242324829</v>
+        <v>0.9094282388687134</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570423722267151</v>
+        <v>0.8560332655906677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608491539955139</v>
+        <v>0.6593944430351257</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013246297836304</v>
+        <v>0.900807797908783</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03228002292548469</v>
       </c>
       <c r="C4" t="n">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>10228677</v>
+        <v>1442905</v>
       </c>
       <c r="E4" t="n">
-        <v>26874774</v>
+        <v>1625968</v>
       </c>
       <c r="F4" t="n">
-        <v>1988600</v>
+        <v>211201</v>
       </c>
       <c r="G4" t="n">
-        <v>139566</v>
+        <v>23309</v>
       </c>
       <c r="H4" t="n">
-        <v>232548</v>
+        <v>38526</v>
       </c>
       <c r="I4" t="n">
-        <v>22971</v>
+        <v>3533</v>
       </c>
       <c r="J4" t="n">
-        <v>1138</v>
+        <v>131</v>
       </c>
       <c r="K4" t="n">
-        <v>11180826</v>
+        <v>1633801</v>
       </c>
       <c r="L4" t="n">
-        <v>12133406</v>
+        <v>1517999</v>
       </c>
       <c r="M4" t="n">
-        <v>3837387</v>
+        <v>459926</v>
       </c>
       <c r="N4" t="n">
-        <v>986459</v>
+        <v>127158</v>
       </c>
       <c r="O4" t="n">
-        <v>1790839</v>
+        <v>227325</v>
       </c>
       <c r="P4" t="n">
-        <v>359460</v>
+        <v>29916</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999924898147583</v>
+        <v>0.9999896287918091</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8418688178062439</v>
+        <v>0.7454434037208557</v>
       </c>
       <c r="S4" t="n">
-        <v>0.684747040271759</v>
+        <v>0.5011123418807983</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5776407718658447</v>
+        <v>0.3360805809497833</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2243915945291519</v>
+        <v>0.05776796117424965</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6232532262802124</v>
+        <v>0.3624123334884644</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6735469102859497</v>
+        <v>0.3092822432518005</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2487043</v>
+        <v>211876</v>
       </c>
       <c r="Z4" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AA4" t="n">
-        <v>996591</v>
+        <v>84107</v>
       </c>
       <c r="AB4" t="n">
-        <v>66559</v>
+        <v>5676</v>
       </c>
       <c r="AC4" t="n">
-        <v>13785</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2662651</v>
+        <v>226691</v>
       </c>
       <c r="AG4" t="n">
-        <v>3470529</v>
+        <v>290052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1592369</v>
+        <v>134350</v>
       </c>
       <c r="AI4" t="n">
-        <v>362962</v>
+        <v>30569</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600021</v>
+        <v>50394</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565883874893188</v>
+        <v>0.9556406140327454</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910810112953186</v>
+        <v>0.9111921787261963</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576045632362366</v>
+        <v>0.8568375706672668</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612026691436768</v>
+        <v>0.6597936749458313</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016525745391846</v>
+        <v>0.9012390971183777</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>156</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>682781</v>
+        <v>139829</v>
       </c>
       <c r="E5" t="n">
-        <v>3311068</v>
+        <v>396818</v>
       </c>
       <c r="F5" t="n">
-        <v>6123893</v>
+        <v>283876</v>
       </c>
       <c r="G5" t="n">
-        <v>303872</v>
+        <v>35291</v>
       </c>
       <c r="H5" t="n">
-        <v>739550</v>
+        <v>80113</v>
       </c>
       <c r="I5" t="n">
-        <v>80520</v>
+        <v>9578</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8243077</v>
+        <v>1029258</v>
       </c>
       <c r="L5" t="n">
-        <v>12612529</v>
+        <v>1719500</v>
       </c>
       <c r="M5" t="n">
-        <v>5117947</v>
+        <v>661655</v>
       </c>
       <c r="N5" t="n">
-        <v>813255</v>
+        <v>83608</v>
       </c>
       <c r="O5" t="n">
-        <v>2542007</v>
+        <v>349155</v>
       </c>
       <c r="P5" t="n">
-        <v>960700</v>
+        <v>153080</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999942183494568</v>
+        <v>0.9999919533729553</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9008758068084717</v>
+        <v>0.8369182944297791</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8737163543701172</v>
+        <v>0.8017404675483704</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9542990922927856</v>
+        <v>0.931316077709198</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9908156991004944</v>
+        <v>0.9870930314064026</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9778885841369629</v>
+        <v>0.9646972417831421</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9932629466056824</v>
+        <v>0.9887936115264893</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>96751</v>
+        <v>8160</v>
       </c>
       <c r="Z5" t="n">
-        <v>1032439</v>
+        <v>87923</v>
       </c>
       <c r="AA5" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AB5" t="n">
-        <v>119853</v>
+        <v>10057</v>
       </c>
       <c r="AC5" t="n">
-        <v>350460</v>
+        <v>29344</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2547251</v>
+        <v>211245</v>
       </c>
       <c r="AG5" t="n">
-        <v>3564799</v>
+        <v>303005</v>
       </c>
       <c r="AH5" t="n">
-        <v>1607107</v>
+        <v>136125</v>
       </c>
       <c r="AI5" t="n">
-        <v>364110</v>
+        <v>30678</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604478</v>
+        <v>50885</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973412811756134</v>
+        <v>0.9731814861297607</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964097261428833</v>
+        <v>0.9636821150779724</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836724400520325</v>
+        <v>0.9834365248680115</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962896108627319</v>
+        <v>0.9962493181228638</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938532114028931</v>
+        <v>0.9937978386878967</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983713626861572</v>
+        <v>0.9983611106872559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>184869</v>
+        <v>24615</v>
       </c>
       <c r="E6" t="n">
-        <v>265379</v>
+        <v>27422</v>
       </c>
       <c r="F6" t="n">
-        <v>252595</v>
+        <v>22392</v>
       </c>
       <c r="G6" t="n">
-        <v>260338</v>
+        <v>6461</v>
       </c>
       <c r="H6" t="n">
-        <v>99637</v>
+        <v>8340</v>
       </c>
       <c r="I6" t="n">
-        <v>10616</v>
+        <v>824</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78306</v>
+        <v>6619</v>
       </c>
       <c r="Z6" t="n">
-        <v>64303</v>
+        <v>5393</v>
       </c>
       <c r="AA6" t="n">
-        <v>131730</v>
+        <v>11143</v>
       </c>
       <c r="AB6" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AC6" t="n">
-        <v>83993</v>
+        <v>7037</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>78172</v>
+        <v>23888</v>
       </c>
       <c r="E7" t="n">
-        <v>549660</v>
+        <v>108829</v>
       </c>
       <c r="F7" t="n">
-        <v>1217643</v>
+        <v>150083</v>
       </c>
       <c r="G7" t="n">
-        <v>452684</v>
+        <v>50748</v>
       </c>
       <c r="H7" t="n">
-        <v>3583920</v>
+        <v>163839</v>
       </c>
       <c r="I7" t="n">
-        <v>243745</v>
+        <v>15596</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9720</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358302</v>
+        <v>30228</v>
       </c>
       <c r="AB7" t="n">
-        <v>91626</v>
+        <v>7747</v>
       </c>
       <c r="AC7" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>6327</v>
+        <v>2564</v>
       </c>
       <c r="E8" t="n">
-        <v>57016</v>
+        <v>13918</v>
       </c>
       <c r="F8" t="n">
-        <v>129069</v>
+        <v>28489</v>
       </c>
       <c r="G8" t="n">
-        <v>67699</v>
+        <v>13072</v>
       </c>
       <c r="H8" t="n">
-        <v>700236</v>
+        <v>95010</v>
       </c>
       <c r="I8" t="n">
-        <v>1361895</v>
+        <v>40970</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
